--- a/03_Tools/Satelliten_Monitor_v4.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v4.0.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="O2" s="35" t="inlineStr">
         <is>
-          <t>Stand: 09.06.2026 (Tier-System eingeführt; NOW/KYCCF/ZETA neu aufgenommen – Vollanalyse ausstehend; VEEV/COST verkauft &amp; entfernt)  |  Broker: Scalable Capital  |  Slots: 13/13</t>
+          <t>Stand: 13.06.2026 (KYCCF O3-Vollanalyse 67/D3 — JGAAP-Primaerquelle; NOW/ZETA Vollanalyse ausstehend; VEEV/COST entfernt)  |  Broker: Scalable Capital  |  Slots: 13/13</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E3" s="42" t="inlineStr">
         <is>
-          <t>Vollanalysiert: 10 / 13  |  Ausstehend: 3 / 13 (KYCCF, NOW, ZETA)</t>
+          <t>Vollanalysiert: 11 / 13  |  Ausstehend: 2 / 13 (NOW, ZETA)</t>
         </is>
       </c>
       <c r="H3" s="43" t="inlineStr">
@@ -1778,36 +1778,66 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>[Analyse ausstehend]</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="11" t="n"/>
+          <t>~38 Fwd P/E / 47x P/FCF [V 13.06.]</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>19.9% GF / op-ROIC &gt;100% [V 13.06.]</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>83.0% [V 13.06.]</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>6.6% [V 13.06.]</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Wide [V 13.06.]</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="11" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>[ausstehend]</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="n"/>
+          <t>67 / DEFCON 3</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>O3 Initial 13.06.</t>
+        </is>
+      </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>● NEU 06.06.2026 | Tier 2 (SOLL 32€) | Stammdaten erfasst, Vollanalyse ausstehend</t>
+          <t>● DEFCON 3 / ✅ Volle Tier-Rate 32€ (Tier 2; D3=1.0) | O3-Vollanalyse 13.06. (JGAAP)</t>
         </is>
       </c>
       <c r="O12" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="14" t="n"/>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>Q1 FY27 ~29.07.</t>
+        </is>
+      </c>
+      <c r="Q12" s="14" t="n">
+        <v>46186</v>
+      </c>
       <c r="R12" s="8">
         <f>IF(Q12="","",TODAY()-Q12)</f>
         <v/>
       </c>
-      <c r="S12" s="15" t="n"/>
+      <c r="S12" s="15" t="inlineStr">
+        <is>
+          <t>[V 13.06.] O3-Vollanalyse Score 67/D3 (Primärquelle JGAAP FY26 ended 31.03.2026, 6861.T). Fwd-P/E+P/FCF QT-hart-0 (Wide-Moat); Bilanz 9/9 Netto-Cash EQ-Ratio 94,6%; CapEx/OCF 6,6%; ROIC 7/8 (GF 19,9% vs WACC 5,54%, Cash-verwaessert op&gt;100%); OpM 51%. Moat 18/20 Wide. Kein FLAG. Near-Twin ASML 68.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="141.95" customHeight="1" s="34">
       <c r="B13" s="9" t="inlineStr">

--- a/03_Tools/Satelliten_Monitor_v4.0.xlsx
+++ b/03_Tools/Satelliten_Monitor_v4.0.xlsx
@@ -1600,27 +1600,27 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">~62 (von 74,4 am 30.04. runter)  </t>
+          <t>43,12 (von ~62 am 04.06. runter) [V 03.09.]</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>5.54% GAAP / 51.1% §410-bereinigt [04.06.]</t>
+          <t>6,72% GAAP-Q / 52,8% §410-bereinigt [03.09.]</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">~67,8% (FY2025 GAAP) · Q2 FY26 reported 77,1%       </t>
+          <t>75,5% TTM · Q3 FY26 reported 75,0% (Mix-Dilution XPU-Memory)</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">~24%   FY2022 $33,2B → FY2025 $63,9B (inkl. VMware)   </t>
+          <t>~34%   FY2022 $33,2B → TTM $89,1B (AI-Ramp)</t>
         </is>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/10 Wide (carryover 30.04.) · Morningstar Wide bestätigt 06.06.   </t>
+          <t>8/10 Wide (carryover 30.04.) · Q3-Call 02.09.: SerDes-IP, Advanced Packaging, Time-to-Market ohne Respins</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
-          <t>56 / DEFCON 2</t>
+          <t>59 / DEFCON 2</t>
         </is>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>Δ-31 30.04. (Quality-Trap)</t>
+          <t>Δ+3 03.09. (kursgetrieben)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>● FLAG: Insider-Selling 90d $106.4M (5× Schwelle, insider_intel.py 30.04.) | OpenInsider 9 Tx „S - Sale" ohne 10b5-1-Suffix | Aktiviert 27.04.2026 | Vollanalyse 30.04. Score 84→53 (D4→D2) | FLAG aktiv unverändert | Sparrate 0€</t>
+          <t>● FLAG: Insider-Selling 90d $33,69M (weiterhin &gt; $20M-Schwelle) | $29,19M davon allein Brazeal/CLO in 3 Tranchen (25.06./08.07./10.07.) ohne 10b5-1 | Plan-Verkaeufe $250M/90d ausgeschlossen | Aktiviert 27.04.2026 | Q3-Vollanalyse 03.09. Score 56→59 | FLAG aktiv unveraendert | Sparrate 0€</t>
         </is>
       </c>
       <c r="O10" s="3" t="n">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="P10" s="18" t="inlineStr">
         <is>
-          <t>Q2 FY26 Earnings ~Juni 2026</t>
+          <t>Q4 FY26 Earnings 09.12.2026 (amc)</t>
         </is>
       </c>
       <c r="Q10" s="21" t="n">
-        <v>46177</v>
+        <v>46268</v>
       </c>
       <c r="R10" s="8">
         <f>IF(Q10="","",TODAY()-Q10)</f>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>● ~68x live (V 30.04.: 74,4)</t>
+          <t>● 43,1x (V 03.09.; 04.06.: ~62)</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>● 3,98% GAAP (§410: 45,7%)</t>
+          <t>● 6,72% GAAP-Q (§410: 52,8%)</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I9" s="28" t="inlineStr">
         <is>
-          <t>Score 53 / D2 (V 30.04., Δ-31). Quality-Trap voll aktiv. Insider-Selling 90d $106,4M. Sparrate 0€.</t>
+          <t>Score 59 / D2 (V 03.09., Δ+3 — kursgetrieben, nicht operativ). P/FCF 43,1 bleibt QT-hart-0; Fwd P/E 20,65 verlaesst den Korridor 22-30. Insider-Selling 90d $33,69M &gt; $20M. Sparrate 0€.</t>
         </is>
       </c>
       <c r="J9">
